--- a/campaign_stats.xlsx
+++ b/campaign_stats.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -686,6 +686,114 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-25 07:14:16</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0993830093</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-25 07:14:17</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0993706980</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-25 07:20:55</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0993215852</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-25 07:20:59</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0993214048</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/campaign_stats.xlsx
+++ b/campaign_stats.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,6 +794,87 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-25 07:22:06</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0993214048</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-25 07:22:06</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0993215852</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-25 07:22:07</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0993081418</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/campaign_stats.xlsx
+++ b/campaign_stats.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,6 +875,168 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-25 07:30:17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0993690087</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-25 07:34:23</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0993083590</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-25 07:34:48</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0993830094</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-25 07:39:15</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0993706984</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-25 07:39:15</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0993983795</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-25 07:39:48</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0993214145</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/campaign_stats.xlsx
+++ b/campaign_stats.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1037,6 +1037,141 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-25 07:41:45</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0993706984</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-25 07:49:11</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0993013929</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-25 07:49:15</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0993367828</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-25 07:50:49</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0993367828</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-25 07:50:49</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0993013929</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/campaign_stats.xlsx
+++ b/campaign_stats.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1172,6 +1172,195 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-25 07:54:14</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0993716780</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-25 08:03:52</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0993013919</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-25 08:04:10</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0993309252</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-25 08:04:29</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0993013919</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-25 08:04:29</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0993309252</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-25 08:04:49</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0993706283</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-06-25 08:05:00</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0993706283</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/campaign_stats.xlsx
+++ b/campaign_stats.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1361,6 +1361,172 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:25:02</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0993740087</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Lỗi ghi file sdt: [Errno 13] Permission denied: 'sdt_da_ton_tai.txt'</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:29:05</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0993143202</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:29:06</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0993205280</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:29:08</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0993196081</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:29:11</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0993808691</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/campaign_stats.xlsx
+++ b/campaign_stats.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1510,7 +1510,6 @@
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1522,6 +1521,854 @@
         </is>
       </c>
       <c r="G40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:31:34</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0993196081</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>❌ Reconnect timeout or stopped by user.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:32:04</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0993692482</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:36:10</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0993808390</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:36:13</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0993280454</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:36:15</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0993281040</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:46:14</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0993015414</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>❌ Timeout waiting for text ['TRIGGER', 'adb shell am broadcast', 'com.autopee']</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:46:27</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0993310010</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:46:46</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0993068575</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:46:46</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0993140080</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:46:47</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0993017404</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:46:54</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0993205284</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:47:25</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0993015414</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TERMINATED</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>❌ Reconnect timeout or stopped by user.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:53:26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0993691581</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:53:38</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0993368565</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:53:48</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0993140232</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:53:48</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0993725583</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:53:58</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0993143616</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:00:25</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0993068565</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:00:51</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0993016393</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:00:54</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0993031929</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:01:20</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0993692481</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:01:27</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0993192387</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:02:42</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0993367858</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:05:10</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0993720083</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:07:52</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0993018434</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:12:54</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0993293343</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>

--- a/campaign_stats.xlsx
+++ b/campaign_stats.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2357,7 +2357,6 @@
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2371,6 +2370,2286 @@
       <c r="G66" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:44:43</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0993706187</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Không nhận được biên lai gửi SMS.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:44:47</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0993142919</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Không nhận được biên lai gửi SMS.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:44:48</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0993306696</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Không nhận được biên lai gửi SMS.</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:47:57</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0993205985</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:47:58</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0993084131</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:51:22</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0993140242</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Không nhận được biên lai gửi SMS.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:51:34</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0993143525</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Không nhận được biên lai gửi SMS.</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:51:41</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0993252393</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:51:55</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0993367787</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:54:20</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0993368707</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Không nhận được biên lai gửi SMS.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:54:53</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0993360090</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Không nhận được biên lai gửi SMS.</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:55:29</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0993716680</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Không nhận được biên lai gửi SMS.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:58:38</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0993015464</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:58:40</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0993142343</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:59:12</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0993317656</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Không nhận được biên lai gửi SMS.</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:00:02</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0993368707</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Reset 4G failed: ADB never went offline after retries.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:01:52</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0993205287</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:02:14</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0993317090</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Không nhận được biên lai gửi SMS.</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:02:47</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0993068505</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Không nhận được biên lai gửi SMS.</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:05:46</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0993368707</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Reset 4G failed: ADB never went offline after retries.</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:06:12</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0993808693</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:08:44</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0993750747</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:09:53</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0993367737</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:09:58</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0993808693</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Reset 4G failed: ADB never went offline after retries.</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:10:48</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0993750787</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>TERMINATED</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>⚠️ PHÁT HIỆN THIẾT BỊ TREO/LAG (UI Dump thất bại 4 lần liên tiếp). Ép dừng tiến trình để tránh kẹt số!</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:12:13</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0993032616</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:13:38</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0993750747</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>TERMINATED</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>❌ Network unavailable after 210s - aborting Zalo launch</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:13:40</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0993068505</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>TERMINATED</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>❌ Network unavailable after 550s - aborting Zalo launch</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:13:42</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0993032616</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>TERMINATED</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>❌ Network unavailable after 4s - aborting Zalo launch</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:17:04</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0993309525</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:33:29</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0993752393</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>❌ Thất bại nhận OTP từ Firefox - Bỏ qua.</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:35:36</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0993143626</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:35:40</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0993205289</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:35:44</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0993706784</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:35:53</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0993298202</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:36:40</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>0993363050</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:40:34</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0993190087</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:42:29</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>0993140020</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:42:42</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>0993383414</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:42:59</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0993368717</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:47:24</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>0993197782</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:49:30</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>0993013525</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:49:38</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>0993273020</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:49:45</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>0993716683</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:51:54</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>0993750767</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>❌ Skip screen timeout</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:52:16</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>0993716683</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>❌ Reconnect timeout or stopped by user.</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:54:17</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0993716683</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>❌ Reconnect timeout or stopped by user.</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:56:18</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>0993716683</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>❌ Reconnect timeout or stopped by user.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:56:25</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>0993383191</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:56:45</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>0993140090</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:58:19</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>0993716683</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>❌ Reconnect timeout or stopped by user.</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:59:46</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>0993808294</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:00:21</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>0993716683</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>❌ Reconnect timeout or stopped by user.</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:02:22</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>0993716683</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>❌ Reconnect timeout or stopped by user.</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:03:17</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>0993143505</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:03:53</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>0993715687</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:06:50</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>0993017303</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:09:06</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>0993691782</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:09:18</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>0993120575</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:09:26</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>0993017969</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:09:30</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>0993017969</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>TERMINATED</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:09:31</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>0993691782</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>TERMINATED</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:09:32</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>0993120575</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>TERMINATED</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:10:13</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>0993017515</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:10:52</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>0993017414</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:11:06</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>0993017515</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>TERMINATED</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>❌ Reconnect timeout or stopped by user.</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:11:06</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>0993017414</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>TERMINATED</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/campaign_stats.xlsx
+++ b/campaign_stats.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1784,7 +1784,6 @@
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1796,6 +1795,2568 @@
         </is>
       </c>
       <c r="G42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:21:03</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0993192284</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:22:05</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0993017919</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:24:02</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0993725584</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>❌ Thất bại nhận OTP từ Firefox - Bỏ qua.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:26:28</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0993741180</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:28:11</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0993019929</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:29:07</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0993297898</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:30:27</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0993091505</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>❌ Thất bại Captcha sau 5 lần.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:30:57</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0993280565</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:31:48</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0993140030</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:35:26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0993851497</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:36:34</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0993316989</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:37:35</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0993317020</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:37:50</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0993143515</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:38:48</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0993016242</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:42:05</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0993716083</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Timeout/Lỗi màn sau captcha: TIMEOUT</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:42:29</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0993692480</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:43:31</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0993750959</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:44:41</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0993142353</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:44:49</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0993716083</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>❌ Timeout waiting for text ['Phone number', 'Phone number', 'Enter phone number']</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:44:50</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0993235652</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:49:32</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0993716685</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:50:31</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0993015474</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:51:41</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0993142595</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:51:52</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0993017393</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:52:02</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0993120858</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:55:01</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0993716685</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>❌ Reconnect timeout or stopped by user.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:57:35</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0993281626</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:58:57</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0993360898</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:58:58</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0993041525</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:59:07</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0993140070</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:02:01</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0993752404</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Không nhận được biên lai gửi SMS.</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:03:52</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0993310282</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>❌ Thất bại nhận OTP từ Firefox - Bỏ qua.</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:04:21</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0993242151</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:05:58</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0993316303</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:06:03</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0993383282</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:09:04</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0993750737</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Không nhận được biên lai gửi SMS.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:10:56</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0993740081</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:11:18</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0993165392</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:12:54</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0993298242</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:13:05</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0993082327</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:16:07</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0993205680</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:17:59</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0993715683</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:19:59</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0993363404</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:20:17</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0993280464</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:22:18</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0993156295</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:23:08</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0993340040</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:23:56</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0993706281</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Không nhận được biên lai gửi SMS.</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:24:58</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0993716782</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:27:01</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0993291484</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:29:23</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0993143080</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:30:20</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0993196780</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:30:49</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0993298232</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:32:07</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0993368232</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:34:04</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0993368272</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:36:22</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0993752767</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:36:44</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0993298272</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:37:33</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0993298131</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:37:47</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0993318323</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:39:08</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0993290767</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:43:21</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>0993319909</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:44:02</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0993319636</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:44:45</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>0993752787</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:44:46</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>0993340292</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:47:32</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0993693287</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Không nhận được biên lai gửi SMS.</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:48:14</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>0993297616</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:50:25</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>0993147670</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:52:25</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>0993691485</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Không nhận được biên lai gửi SMS.</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:53:09</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>0993281929</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:54:27</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>0993340373</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:55:51</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>0993142565</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Không nhận được biên lai gửi SMS.</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:57:21</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0993290636</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:59:35</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>0993280434</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Không nhận được biên lai gửi SMS.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-06-25 15:00:04</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>0993017616</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-06-25 15:00:06</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>0993182094</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-06-25 15:01:22</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>0993017313</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-06-25 15:04:27</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>0993319252</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-06-25 15:06:37</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>0993296898</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-06-25 15:07:03</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>0993271535</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
